--- a/EN/rutina_21_3_dias_mujer_lower_casa_medio_avanzado.xlsx
+++ b/EN/rutina_21_3_dias_mujer_lower_casa_medio_avanzado.xlsx
@@ -412,11 +412,12 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="str">
-        <x:v>PLANTILLA DE ENTRENAMIENTO · TRUELIFT</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2"/>
+      <x:c r="A1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">PLANTILLA DE ENTRENAMIENTO · TRUELIFT</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="inlineStr">
         <x:is>
@@ -429,212 +430,203 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="4"/>
-    <x:row r="5"/>
     <x:row r="6">
-      <x:c r="A6" t="inlineStr">
+      <x:c r="A6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Rutina generada:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="0" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Routine 21 - 3 days - at-home lower-body-focused hypertrophy - women - intermediate to advanced</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Objetivo:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="0" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Hypertrophy with an emphasis on glutes and lower body (two leg days and one upper day) at higher intensities, for training at home with an adjustable bench, dumbbells, barbell and plates, rack, and pull-up bar.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notas de diseño:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="0" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Only exercises compatible with the listed equipment. Squats and hip thrusts use a top set with back-off sets (apply the indicated % and RIR). Leave at least one rest day between sessions. Minimum equipment: dumbbells, barbell, plates, bench and rack. If the rack has no pull-up bar, replace pull-ups with “Pullover con mancuerna” or “Remo invertido” (barbell on the low pins) and “Elevación de piernas colgado” with “Crunch inverso”. Library swap: “Gemelo de pie con peso corporal” → “Gemelo a una pierna con mancuerna” so calf work can keep progressing with load.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Progresión recomendada:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="0" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Double progression: when all sets reach the top of the range at the prescribed RIR, increase the load by the smallest possible amount and return to the bottom of the range.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Intensificadores:</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="0" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Superset = alternate the sets of the two linked exercises with no rest between them; drop set = after the last set, successive load drops with no rest. Each row allows only one method (top+back, superset or drop set). Day 1: superset Abducción de cadera tumbado de lado + Gemelo a una pierna con mancuerna. Day 2: superset Elevación lateral con mancuernas + Curl con mancuernas. Day 3: superset Patada lateral en cuadrupedia + Dead bug.</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Cómo usar esta plantilla (rellénala en Excel o LibreOffice):</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="inlineStr">
+    <x:row r="13">
+      <x:c r="A13" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1) Elige arriba el sistema: "simple" o "doble".</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="inlineStr">
+    <x:row r="14">
+      <x:c r="A14" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">2) En cada pestaña Día 1..Día 5: nombre de la sesión (B1) y ejercicios.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="inlineStr">
+    <x:row r="15">
+      <x:c r="A15" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">3) Elige PATRÓN (A) y, según el patrón, el EJERCICIO (B).</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="inlineStr">
+    <x:row r="16">
+      <x:c r="A16" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">   Indica SERIES, RIR objetivo y repeticiones.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="inlineStr">
+    <x:row r="17">
+      <x:c r="A17" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">   - SIMPLE: solo "Reps mín / objetivo".</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="inlineStr">
+    <x:row r="18">
+      <x:c r="A18" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">   - DOBLE: "Reps mín" y "Reps máx".</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="inlineStr">
+    <x:row r="19">
+      <x:c r="A19" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">4) DESCANSO (min): admite medios minutos (0,5).</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="inlineStr">
+    <x:row r="20">
+      <x:c r="A20" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">5) Deja el PATRÓN en "(Ninguno)" en las filas que no uses.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="inlineStr">
+    <x:row r="21">
+      <x:c r="A21" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">6) Usa entre 2 y 5 días.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="inlineStr">
+    <x:row r="22">
+      <x:c r="A22" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">7) Guarda y pulsa "Importar" en la app.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="inlineStr">
+    <x:row r="23">
+      <x:c r="A23" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">8) TOP+BACK (opcional, columna H) = "sí": la 1.ª serie es la top</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="inlineStr">
+    <x:row r="24">
+      <x:c r="A24" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">   (fija la progresión) y el resto back-offs con el % menos de peso (I)</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="inlineStr">
+    <x:row r="25">
+      <x:c r="A25" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">   hasta el RIR de la columna J. Vacío o "no" = series rectas.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="inlineStr">
+    <x:row r="26">
+      <x:c r="A26" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">9) SUPERSERIE (columna K): pon el mismo número (1, 2…) en dos filas</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="inlineStr">
+    <x:row r="27">
+      <x:c r="A27" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">   seguidas para enlazarlas y alternar sus series sin descanso.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="inlineStr">
+    <x:row r="28">
+      <x:c r="A28" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">10) DROP SET (columna L) = "sí": tras la última serie, bajadas de peso</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="inlineStr">
+    <x:row r="29">
+      <x:c r="A29" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">    seguidas del % de la columna M, sin descanso.</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="inlineStr">
+    <x:row r="30">
+      <x:c r="A30" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">11) Cada fila admite solo UNA modalidad: top+back, drop set o superserie;</x:t>
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="inlineStr">
+    <x:row r="31">
+      <x:c r="A31" s="0" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">    el Excel bloquea las combinaciones y la app deshace las que lleguen.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FICHA DE LA RUTINA</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Rutina generada:</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B28" s="0" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Routine 21 - 3 days - at-home lower-body-focused hypertrophy - women - intermediate to advanced</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Objetivo:</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B29" s="0" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Hypertrophy with an emphasis on glutes and lower body (two leg days and one upper day) at higher intensities, for training at home with an adjustable bench, dumbbells, barbell and plates, rack, and pull-up bar.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Notas de diseño:</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B30" s="0" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Only exercises compatible with the listed equipment. Squats and hip thrusts use a top set with back-off sets (apply the indicated % and RIR). Leave at least one rest day between sessions. Minimum equipment: dumbbells, barbell, plates, bench and rack. If the rack has no pull-up bar, replace pull-ups with “Pullover con mancuerna” or “Remo invertido” (barbell on the low pins) and “Elevación de piernas colgado” with “Crunch inverso”. Library swap: “Gemelo de pie con peso corporal” → “Gemelo a una pierna con mancuerna” so calf work can keep progressing with load.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Progresión recomendada:</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B31" s="0" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Double progression: when all sets reach the top of the range at the prescribed RIR, increase the load by the smallest possible amount and return to the bottom of the range.</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Intensificadores:</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B32" s="0" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Superset = alternate the sets of the two linked exercises with no rest between them; drop set = after the last set, successive load drops with no rest. Each row allows only one method (top+back, superset or drop set). Day 1: superset Abducción de cadera tumbado de lado + Gemelo a una pierna con mancuerna. Day 2: superset Elevación lateral con mancuernas + Curl con mancuernas. Day 3: superset Patada lateral en cuadrupedia + Dead bug.</x:t>
         </x:is>
       </x:c>
     </x:row>
